--- a/NWJSSP_ArturoMurgueytio_Constructivo.xlsx
+++ b/NWJSSP_ArturoMurgueytio_Constructivo.xlsx
@@ -1503,7 +1503,7 @@
         <v>54669545</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>7680</v>
+        <v>8141</v>
       </c>
     </row>
     <row r="2">
@@ -5529,7 +5529,7 @@
         <v>5021734</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>637</v>
+        <v>737</v>
       </c>
     </row>
     <row r="2">
@@ -9555,7 +9555,7 @@
         <v>6324039</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>3517</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="2">
@@ -12681,7 +12681,7 @@
         <v>4999471</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2">
@@ -13107,7 +13107,7 @@
         <v>6147364</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2">
@@ -13533,7 +13533,7 @@
         <v>504826</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2">
@@ -13959,7 +13959,7 @@
         <v>595659</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2">
@@ -14295,7 +14295,7 @@
         <v>53592</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
@@ -14477,7 +14477,7 @@
         <v>8140</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
@@ -14543,7 +14543,7 @@
         <v>9489</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
@@ -14619,7 +14619,7 @@
         <v>10259</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2">
@@ -14725,7 +14725,7 @@
         <v>13814</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
@@ -15811,7 +15811,7 @@
         <v>500517938</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>160571</v>
+        <v>157891</v>
       </c>
     </row>
     <row r="2">
@@ -19837,7 +19837,7 @@
         <v>558041571</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>194711</v>
+        <v>195771</v>
       </c>
     </row>
     <row r="2">
@@ -23863,7 +23863,7 @@
         <v>50036317</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>6663</v>
+        <v>7048</v>
       </c>
     </row>
     <row r="2">

--- a/NWJSSP_ArturoMurgueytio_Constructivo.xlsx
+++ b/NWJSSP_ArturoMurgueytio_Constructivo.xlsx
@@ -13,12 +13,10 @@
     <sheet name="ft10r" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ft20" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="tai_j100_m100_1" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="tai_j100_m100_1r" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="tai_j100_m10_1" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="tai_j10_m10_1" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="tai_j10_m10_1r" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="tai_j100_m10_1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="tai_j100_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j10_m10_1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tai_j10_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,498 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="12" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
-    <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="12" customWidth="1" min="43" max="43"/>
-    <col width="12" customWidth="1" min="44" max="44"/>
-    <col width="12" customWidth="1" min="45" max="45"/>
-    <col width="12" customWidth="1" min="46" max="46"/>
-    <col width="12" customWidth="1" min="47" max="47"/>
-    <col width="12" customWidth="1" min="48" max="48"/>
-    <col width="12" customWidth="1" min="49" max="49"/>
-    <col width="12" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
-    <col width="12" customWidth="1" min="52" max="52"/>
-    <col width="12" customWidth="1" min="53" max="53"/>
-    <col width="12" customWidth="1" min="54" max="54"/>
-    <col width="12" customWidth="1" min="55" max="55"/>
-    <col width="12" customWidth="1" min="56" max="56"/>
-    <col width="12" customWidth="1" min="57" max="57"/>
-    <col width="12" customWidth="1" min="58" max="58"/>
-    <col width="12" customWidth="1" min="59" max="59"/>
-    <col width="12" customWidth="1" min="60" max="60"/>
-    <col width="12" customWidth="1" min="61" max="61"/>
-    <col width="12" customWidth="1" min="62" max="62"/>
-    <col width="12" customWidth="1" min="63" max="63"/>
-    <col width="12" customWidth="1" min="64" max="64"/>
-    <col width="12" customWidth="1" min="65" max="65"/>
-    <col width="12" customWidth="1" min="66" max="66"/>
-    <col width="12" customWidth="1" min="67" max="67"/>
-    <col width="12" customWidth="1" min="68" max="68"/>
-    <col width="12" customWidth="1" min="69" max="69"/>
-    <col width="12" customWidth="1" min="70" max="70"/>
-    <col width="12" customWidth="1" min="71" max="71"/>
-    <col width="12" customWidth="1" min="72" max="72"/>
-    <col width="12" customWidth="1" min="73" max="73"/>
-    <col width="12" customWidth="1" min="74" max="74"/>
-    <col width="12" customWidth="1" min="75" max="75"/>
-    <col width="12" customWidth="1" min="76" max="76"/>
-    <col width="12" customWidth="1" min="77" max="77"/>
-    <col width="12" customWidth="1" min="78" max="78"/>
-    <col width="12" customWidth="1" min="79" max="79"/>
-    <col width="12" customWidth="1" min="80" max="80"/>
-    <col width="12" customWidth="1" min="81" max="81"/>
-    <col width="12" customWidth="1" min="82" max="82"/>
-    <col width="12" customWidth="1" min="83" max="83"/>
-    <col width="12" customWidth="1" min="84" max="84"/>
-    <col width="12" customWidth="1" min="85" max="85"/>
-    <col width="12" customWidth="1" min="86" max="86"/>
-    <col width="12" customWidth="1" min="87" max="87"/>
-    <col width="12" customWidth="1" min="88" max="88"/>
-    <col width="12" customWidth="1" min="89" max="89"/>
-    <col width="12" customWidth="1" min="90" max="90"/>
-    <col width="12" customWidth="1" min="91" max="91"/>
-    <col width="12" customWidth="1" min="92" max="92"/>
-    <col width="12" customWidth="1" min="93" max="93"/>
-    <col width="12" customWidth="1" min="94" max="94"/>
-    <col width="12" customWidth="1" min="95" max="95"/>
-    <col width="12" customWidth="1" min="96" max="96"/>
-    <col width="12" customWidth="1" min="97" max="97"/>
-    <col width="12" customWidth="1" min="98" max="98"/>
-    <col width="12" customWidth="1" min="99" max="99"/>
-    <col width="12" customWidth="1" min="100" max="100"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>595659</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5536</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4678</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4350</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3429</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6199</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3233</v>
-      </c>
-      <c r="R2" t="n">
-        <v>7008</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3955</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4402</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>4976</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>6466</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>484</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>4257</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>3504</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>3851</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>875</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>339</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>3663</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>6680</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>2981</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>155</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>2325</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>3342</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>3699</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>446</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>53592</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>837</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -999,7 +505,7 @@
         <v>63006</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
@@ -1115,7 +621,7 @@
         <v>8140</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
@@ -1257,7 +763,7 @@
         <v>10259</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
@@ -1363,7 +869,7 @@
         <v>13814</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -1546,10 +1052,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n">
-        <v>4999471</v>
+        <v>504826</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>443</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2">
@@ -1611,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1972,10 +1478,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n">
-        <v>6147364</v>
+        <v>595659</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>345</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2">
@@ -1983,70 +1489,70 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4731</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>35087</v>
+        <v>5536</v>
       </c>
       <c r="D2" t="n">
-        <v>31729</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4678</v>
       </c>
       <c r="F2" t="n">
-        <v>55889</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4350</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>13075</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44898</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>51105</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3429</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>6199</v>
       </c>
       <c r="P2" t="n">
-        <v>41151</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3233</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>7008</v>
       </c>
       <c r="S2" t="n">
-        <v>8929</v>
+        <v>3955</v>
       </c>
       <c r="T2" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>30494</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>52190</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -2055,13 +1561,13 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4402</v>
       </c>
       <c r="AB2" t="n">
-        <v>54542</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -2088,16 +1594,16 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>4976</v>
       </c>
       <c r="AL2" t="n">
-        <v>26807</v>
+        <v>6466</v>
       </c>
       <c r="AM2" t="n">
-        <v>55421</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>7151</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -2106,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>57280</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>42343</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>484</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -2124,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>23957</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -2136,28 +1642,28 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>42125</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>53688</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>36310</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1259</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>51643</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>4257</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
@@ -2172,37 +1678,37 @@
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>3504</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>3851</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>22875</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>56972</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>12102</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>3663</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
@@ -2211,31 +1717,31 @@
         <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>6680</v>
       </c>
       <c r="CA2" t="n">
         <v>0</v>
       </c>
       <c r="CB2" t="n">
-        <v>59180</v>
+        <v>2981</v>
       </c>
       <c r="CC2" t="n">
-        <v>17160</v>
+        <v>155</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0</v>
+        <v>2325</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>13537</v>
+        <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>8194</v>
+        <v>0</v>
       </c>
       <c r="CI2" t="n">
         <v>0</v>
@@ -2244,19 +1750,19 @@
         <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>58525</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
         <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>0</v>
+        <v>3342</v>
       </c>
       <c r="CN2" t="n">
         <v>0</v>
       </c>
       <c r="CO2" t="n">
-        <v>12397</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
         <v>0</v>
@@ -2268,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="CS2" t="n">
-        <v>17668</v>
+        <v>3699</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="CU2" t="n">
-        <v>46504</v>
+        <v>0</v>
       </c>
       <c r="CV2" t="n">
         <v>0</v>
@@ -2291,7 +1797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2304,104 +1810,14 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="12" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
-    <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="12" customWidth="1" min="43" max="43"/>
-    <col width="12" customWidth="1" min="44" max="44"/>
-    <col width="12" customWidth="1" min="45" max="45"/>
-    <col width="12" customWidth="1" min="46" max="46"/>
-    <col width="12" customWidth="1" min="47" max="47"/>
-    <col width="12" customWidth="1" min="48" max="48"/>
-    <col width="12" customWidth="1" min="49" max="49"/>
-    <col width="12" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
-    <col width="12" customWidth="1" min="52" max="52"/>
-    <col width="12" customWidth="1" min="53" max="53"/>
-    <col width="12" customWidth="1" min="54" max="54"/>
-    <col width="12" customWidth="1" min="55" max="55"/>
-    <col width="12" customWidth="1" min="56" max="56"/>
-    <col width="12" customWidth="1" min="57" max="57"/>
-    <col width="12" customWidth="1" min="58" max="58"/>
-    <col width="12" customWidth="1" min="59" max="59"/>
-    <col width="12" customWidth="1" min="60" max="60"/>
-    <col width="12" customWidth="1" min="61" max="61"/>
-    <col width="12" customWidth="1" min="62" max="62"/>
-    <col width="12" customWidth="1" min="63" max="63"/>
-    <col width="12" customWidth="1" min="64" max="64"/>
-    <col width="12" customWidth="1" min="65" max="65"/>
-    <col width="12" customWidth="1" min="66" max="66"/>
-    <col width="12" customWidth="1" min="67" max="67"/>
-    <col width="12" customWidth="1" min="68" max="68"/>
-    <col width="12" customWidth="1" min="69" max="69"/>
-    <col width="12" customWidth="1" min="70" max="70"/>
-    <col width="12" customWidth="1" min="71" max="71"/>
-    <col width="12" customWidth="1" min="72" max="72"/>
-    <col width="12" customWidth="1" min="73" max="73"/>
-    <col width="12" customWidth="1" min="74" max="74"/>
-    <col width="12" customWidth="1" min="75" max="75"/>
-    <col width="12" customWidth="1" min="76" max="76"/>
-    <col width="12" customWidth="1" min="77" max="77"/>
-    <col width="12" customWidth="1" min="78" max="78"/>
-    <col width="12" customWidth="1" min="79" max="79"/>
-    <col width="12" customWidth="1" min="80" max="80"/>
-    <col width="12" customWidth="1" min="81" max="81"/>
-    <col width="12" customWidth="1" min="82" max="82"/>
-    <col width="12" customWidth="1" min="83" max="83"/>
-    <col width="12" customWidth="1" min="84" max="84"/>
-    <col width="12" customWidth="1" min="85" max="85"/>
-    <col width="12" customWidth="1" min="86" max="86"/>
-    <col width="12" customWidth="1" min="87" max="87"/>
-    <col width="12" customWidth="1" min="88" max="88"/>
-    <col width="12" customWidth="1" min="89" max="89"/>
-    <col width="12" customWidth="1" min="90" max="90"/>
-    <col width="12" customWidth="1" min="91" max="91"/>
-    <col width="12" customWidth="1" min="92" max="92"/>
-    <col width="12" customWidth="1" min="93" max="93"/>
-    <col width="12" customWidth="1" min="94" max="94"/>
-    <col width="12" customWidth="1" min="95" max="95"/>
-    <col width="12" customWidth="1" min="96" max="96"/>
-    <col width="12" customWidth="1" min="97" max="97"/>
-    <col width="12" customWidth="1" min="98" max="98"/>
-    <col width="12" customWidth="1" min="99" max="99"/>
-    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n">
-        <v>504826</v>
+        <v>53592</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2">
@@ -2424,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>837</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2433,276 +1849,6 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV2" t="n">
         <v>0</v>
       </c>
     </row>
